--- a/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
@@ -902,31 +902,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E6" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
+        <v>44.603977960912829</v>
+      </c>
+      <c r="F6" s="4">
         <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
+        <v>105.39602203908717</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
+        <v>9477.880101042374</v>
+      </c>
+      <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>522.11989895762599</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -934,31 +936,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
+      <c r="D7" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E7" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+        <v>44.113427361741763</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
+        <v>105.88657263825823</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>9371.9935284041167</v>
+      </c>
+      <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>628.00647159588334</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -968,31 +972,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
+        <v>43.620593565485173</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>106.37940643451483</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>9265.6141219696019</v>
+      </c>
+      <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>734.38587803039809</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -1003,31 +1009,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
+      <c r="D9" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E9" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
+        <v>43.125465945331158</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>106.87453405466884</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>9158.7395879149335</v>
+      </c>
+      <c r="H9" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>841.26041208506649</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -1037,31 +1045,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E10" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
+        <v>42.628033825006902</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>107.3719661749931</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>9051.3676217399407</v>
+      </c>
+      <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>948.63237826005934</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -1132,7 +1142,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1167,7 +1177,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>11400</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1202,7 +1212,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>9583.2761230814613</v>
+        <v>9051.3676217399407</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1237,7 +1247,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>416.72387691853874</v>
+        <v>948.63237826005934</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
@@ -1081,103 +1081,109 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46292</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E11" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>42.128286478548382</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>107.87171352145162</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>8943.4959082184887</v>
+      </c>
+      <c r="H11" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1056.5040917815113</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E12" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
+        <v>41.626213130069132</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>108.37378686993087</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>8835.1221213485587</v>
+      </c>
+      <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1164.8778786514413</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46292</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
+        <v>41.121802953527883</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>108.87819704647211</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>8726.2439243020872</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1273.7560756979128</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>10650</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1212,7 +1218,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>9051.3676217399407</v>
+        <v>8726.2439243020872</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1247,7 +1253,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>948.63237826005934</v>
+        <v>1273.7560756979128</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Thongam_Memi_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,105 +1183,111 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>10200</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
+        <v>40.615045072495114</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>109.38495492750488</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>8616.8589693745816</v>
+      </c>
+      <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1383.1410306254184</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8726.2439243020872</v>
+        <v>7836.7755494887006</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E15" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>40.105928559918503</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>109.89407144008149</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>8506.9648979345002</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1493.0351020654998</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1273.7560756979128</v>
+        <v>2163.2244505112994</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
+        <v>39.59444243788738</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>110.40555756211262</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>8396.5593403723869</v>
+      </c>
+      <c r="H16" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1603.4406596276131</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1292,31 +1298,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
+      <c r="D17" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E17" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>39.080575677395949</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>110.91942432260404</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>8285.6399160497822</v>
+      </c>
+      <c r="H17" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1714.3600839502178</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1327,117 +1335,125 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E18" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
+        <v>38.564317198105492</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>111.4356828018945</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>8174.2042332478877</v>
+      </c>
+      <c r="H18" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1825.7957667521123</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46304</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
+        <v>38.045655868105456</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>111.95434413189454</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>8062.249889115993</v>
+      </c>
+      <c r="H19" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1937.750110884007</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
+        <v>37.524580503673427</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>112.47541949632657</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>7949.7744696196669</v>
+      </c>
+      <c r="H20" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2050.2255303803331</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46304</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
+        <v>150</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
+        <v>37.001079869033937</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>112.99892013096607</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>7836.7755494887006</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2163.2244505112994</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
